--- a/codespace/results/ch3_fw3_benchmark_lda_stratified_confusion_matrix.xlsx
+++ b/codespace/results/ch3_fw3_benchmark_lda_stratified_confusion_matrix.xlsx
@@ -509,13 +509,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -548,13 +548,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>77% (n = 44)</t>
+          <t>81% (n = 43)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>83% (n = 18)</t>
+          <t>84% (n = 19)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>

--- a/codespace/results/ch3_fw3_benchmark_lda_stratified_confusion_matrix.xlsx
+++ b/codespace/results/ch3_fw3_benchmark_lda_stratified_confusion_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
